--- a/outputs/24-23.xlsx
+++ b/outputs/24-23.xlsx
@@ -271,8 +271,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -473,2268 +477,2544 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D207"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="n">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>11134</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>11135</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="n">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>11136</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="n">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>11137</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="n">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>11138</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="n">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>11139</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>11140</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="n">
+      <c r="A9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>11141</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="2" t="n">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>11142</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="n">
+      <c r="A11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>11143</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2" t="n">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>11144</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="n">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>11145</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2" t="n">
+      <c r="A14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>11146</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="2" t="n">
+      <c r="A15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>11147</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="2" t="n">
+      <c r="A16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="n">
         <v>11148</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="2" t="n">
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3" t="n">
         <v>11149</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="2" t="n">
+      <c r="A18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="n">
         <v>11150</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="n">
+      <c r="A19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="n">
         <v>11151</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="2" t="n">
+      <c r="A20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3" t="n">
         <v>11152</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="n">
+      <c r="A21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="n">
         <v>11153</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="2" t="n">
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="3" t="n">
         <v>11154</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="2" t="n">
+      <c r="A23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="n">
         <v>11155</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="2" t="n">
+      <c r="A24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="n">
         <v>11156</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="2" t="n">
+      <c r="A25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="3" t="n">
         <v>11157</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="2" t="n">
+      <c r="A26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3" t="n">
         <v>11158</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="2" t="n">
+      <c r="A27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="3" t="n">
         <v>11159</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="2" t="n">
+      <c r="A28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="3" t="n">
         <v>11160</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="2" t="n">
+      <c r="A29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="3" t="n">
         <v>11161</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="2" t="n">
+      <c r="A30" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="3" t="n">
         <v>11162</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2" t="n">
+      <c r="A31" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="n">
         <v>11163</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="2" t="n">
+      <c r="A32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="n">
         <v>11164</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="2" t="n">
+      <c r="A33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="3" t="n">
         <v>11165</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="2" t="n">
+      <c r="A34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="n">
         <v>11166</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="2" t="n">
+      <c r="A35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="3" t="n">
         <v>11167</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="2" t="n">
+      <c r="A36" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="3" t="n">
         <v>11168</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="2" t="n">
+      <c r="A37" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="3" t="n">
         <v>11169</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="2" t="n">
+      <c r="A38" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="3" t="n">
         <v>11170</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="2" t="n">
+      <c r="A39" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="3" t="n">
         <v>11171</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="2" t="n">
+      <c r="A40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="3" t="n">
         <v>11172</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="2" t="n">
+      <c r="A41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="3" t="n">
         <v>11173</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="2" t="n">
+      <c r="A42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="3" t="n">
         <v>11174</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="2" t="n">
+      <c r="A43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="3" t="n">
         <v>11175</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="2" t="n">
+      <c r="A44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="3" t="n">
         <v>11176</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="2" t="n">
+      <c r="A45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="3" t="n">
         <v>11177</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="2" t="n">
+      <c r="A46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="3" t="n">
         <v>11178</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="2" t="n">
+      <c r="A47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="3" t="n">
         <v>11179</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="2" t="n">
+      <c r="A48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="3" t="n">
         <v>11180</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="2" t="n">
+      <c r="A49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="3" t="n">
         <v>11181</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="2" t="n">
+      <c r="A50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="3" t="n">
         <v>11182</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="2" t="n">
+      <c r="A51" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="3" t="n">
         <v>11183</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="2" t="n">
+      <c r="A52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="3" t="n">
         <v>11184</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="2" t="n">
+      <c r="A53" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="3" t="n">
         <v>11185</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="2" t="n">
+      <c r="A54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="3" t="n">
         <v>11186</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" s="2" t="n">
+      <c r="A55" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="3" t="n">
         <v>11187</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="2" t="n">
+      <c r="A56" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="3" t="n">
         <v>11188</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="2" t="n">
+      <c r="A57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="3" t="n">
         <v>11189</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="2" t="n">
+      <c r="A58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="3" t="n">
         <v>11190</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="2" t="n">
+      <c r="A59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="3" t="n">
         <v>11191</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="2" t="n">
+      <c r="A60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="3" t="n">
         <v>11192</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="2" t="n">
+      <c r="A61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="3" t="n">
         <v>11193</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="2" t="n">
+      <c r="A62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="3" t="n">
         <v>11194</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="2" t="n">
+      <c r="A63" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="3" t="n">
         <v>11195</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" s="2" t="n">
+      <c r="A64" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="3" t="n">
         <v>11196</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="2" t="n">
+      <c r="A65" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="3" t="n">
         <v>11197</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="2" t="n">
+      <c r="A66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="3" t="n">
         <v>11198</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="2" t="n">
+      <c r="A67" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="3" t="n">
         <v>11199</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="2" t="n">
+      <c r="A68" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="3" t="n">
         <v>11200</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="2" t="n">
+      <c r="A69" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="3" t="n">
         <v>11201</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B70" s="2" t="n">
+      <c r="A70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="3" t="n">
         <v>11202</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B71" s="2" t="n">
+      <c r="A71" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="3" t="n">
         <v>11203</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B72" s="2" t="n">
+      <c r="A72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="3" t="n">
         <v>11204</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B73" s="2" t="n">
+      <c r="A73" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" s="3" t="n">
         <v>11205</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B74" s="2" t="n">
+      <c r="A74" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="3" t="n">
         <v>11206</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B75" s="2" t="n">
+      <c r="A75" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" s="3" t="n">
         <v>11207</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B76" s="2" t="n">
+      <c r="A76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" s="3" t="n">
         <v>11208</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B77" s="2" t="n">
+      <c r="A77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="3" t="n">
         <v>11209</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78" s="2" t="n">
+      <c r="A78" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="3" t="n">
         <v>11210</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B79" s="2" t="n">
+      <c r="A79" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="3" t="n">
         <v>11211</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" s="2" t="n">
+      <c r="A80" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="3" t="n">
         <v>11212</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B81" s="2" t="n">
+      <c r="A81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B81" s="3" t="n">
         <v>11213</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B82" s="2" t="n">
+      <c r="A82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B82" s="3" t="n">
         <v>11214</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B83" s="2" t="n">
+      <c r="A83" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B83" s="3" t="n">
         <v>11215</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B84" s="2" t="n">
+      <c r="A84" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B84" s="3" t="n">
         <v>11216</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B85" s="2" t="n">
+      <c r="A85" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85" s="3" t="n">
         <v>11217</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B86" s="2" t="n">
+      <c r="A86" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B86" s="3" t="n">
         <v>11218</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B87" s="2" t="n">
+      <c r="A87" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="3" t="n">
         <v>11219</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B88" s="2" t="n">
+      <c r="A88" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88" s="3" t="n">
         <v>11220</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B89" s="2" t="n">
+      <c r="A89" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="3" t="n">
         <v>11221</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B90" s="2" t="n">
+      <c r="A90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" s="3" t="n">
         <v>11222</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B91" s="2" t="n">
+      <c r="A91" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B91" s="3" t="n">
         <v>11223</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B92" s="2" t="n">
+      <c r="A92" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" s="3" t="n">
         <v>11224</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B93" s="2" t="n">
+      <c r="A93" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93" s="3" t="n">
         <v>11225</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B94" s="2" t="n">
+      <c r="A94" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94" s="3" t="n">
         <v>11226</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B95" s="2" t="n">
+      <c r="A95" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="3" t="n">
         <v>11227</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B96" s="2" t="n">
+      <c r="A96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B96" s="3" t="n">
         <v>11228</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B97" s="2" t="n">
+      <c r="A97" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97" s="3" t="n">
         <v>11229</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B98" s="2" t="n">
+      <c r="A98" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B98" s="3" t="n">
         <v>11230</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B99" s="2" t="n">
+      <c r="A99" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B99" s="3" t="n">
         <v>11231</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B100" s="2" t="n">
+      <c r="A100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B100" s="3" t="n">
         <v>11232</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B101" s="2" t="n">
+      <c r="A101" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B101" s="3" t="n">
         <v>11233</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B102" s="2" t="n">
+      <c r="A102" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B102" s="3" t="n">
         <v>11234</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B103" s="2" t="n">
+      <c r="A103" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B103" s="3" t="n">
         <v>11235</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B104" s="2" t="n">
+      <c r="A104" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B104" s="3" t="n">
         <v>11236</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B105" s="2" t="n">
+      <c r="A105" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B105" s="3" t="n">
         <v>11237</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B106" s="2" t="n">
+      <c r="A106" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B106" s="3" t="n">
         <v>11238</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B107" s="2" t="n">
+      <c r="A107" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" s="3" t="n">
         <v>11239</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B108" s="2" t="n">
+      <c r="A108" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B108" s="3" t="n">
         <v>11240</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B109" s="2" t="n">
+      <c r="A109" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B109" s="3" t="n">
         <v>11241</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B110" s="2" t="n">
+      <c r="A110" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B110" s="3" t="n">
         <v>11242</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B111" s="2" t="n">
+      <c r="A111" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B111" s="3" t="n">
         <v>11243</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B112" s="2" t="n">
+      <c r="A112" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B112" s="3" t="n">
         <v>11244</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B113" s="2" t="n">
+      <c r="A113" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B113" s="3" t="n">
         <v>11245</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B114" s="2" t="n">
+      <c r="A114" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B114" s="3" t="n">
         <v>11246</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B115" s="2" t="n">
+      <c r="A115" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B115" s="3" t="n">
         <v>11247</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D115" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B116" s="2" t="n">
+      <c r="A116" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B116" s="3" t="n">
         <v>11248</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D116" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B117" s="2" t="n">
+      <c r="A117" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B117" s="3" t="n">
         <v>11249</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B118" s="2" t="n">
+      <c r="A118" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B118" s="3" t="n">
         <v>11250</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B119" s="2" t="n">
+      <c r="A119" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B119" s="3" t="n">
         <v>11251</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D119" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B120" s="2" t="n">
+      <c r="A120" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B120" s="3" t="n">
         <v>11252</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D120" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B121" s="2" t="n">
+      <c r="A121" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B121" s="3" t="n">
         <v>11253</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B122" s="2" t="n">
+      <c r="A122" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B122" s="3" t="n">
         <v>11254</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D122" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B123" s="2" t="n">
+      <c r="A123" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B123" s="3" t="n">
         <v>11255</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D123" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B124" s="2" t="n">
+      <c r="A124" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B124" s="3" t="n">
         <v>11256</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D124" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B125" s="2" t="n">
+      <c r="A125" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B125" s="3" t="n">
         <v>11257</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D125" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B126" s="2" t="n">
+      <c r="A126" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B126" s="3" t="n">
         <v>11258</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B127" s="2" t="n">
+      <c r="A127" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B127" s="3" t="n">
         <v>11259</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B128" s="2" t="n">
+      <c r="A128" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B128" s="3" t="n">
         <v>11260</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D128" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B129" s="2" t="n">
+      <c r="A129" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B129" s="3" t="n">
         <v>11261</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D129" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B130" s="2" t="n">
+      <c r="A130" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B130" s="3" t="n">
         <v>11262</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D130" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B131" s="2" t="n">
+      <c r="A131" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B131" s="3" t="n">
         <v>11263</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D131" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B132" s="2" t="n">
+      <c r="A132" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B132" s="3" t="n">
         <v>11264</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B133" s="2" t="n">
+      <c r="A133" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B133" s="3" t="n">
         <v>11265</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B134" s="2" t="n">
+      <c r="A134" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B134" s="3" t="n">
         <v>11266</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D134" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B135" s="2" t="n">
+      <c r="A135" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B135" s="3" t="n">
         <v>11267</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B136" s="2" t="n">
+      <c r="A136" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B136" s="3" t="n">
         <v>11268</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D136" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B137" s="2" t="n">
+      <c r="A137" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B137" s="3" t="n">
         <v>11269</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="D137" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B138" s="2" t="n">
+      <c r="A138" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B138" s="3" t="n">
         <v>11270</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="D138" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B139" s="2" t="n">
+      <c r="A139" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B139" s="3" t="n">
         <v>11271</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="D139" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B140" s="2" t="n">
+      <c r="A140" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B140" s="3" t="n">
         <v>11272</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D140" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B141" s="2" t="n">
+      <c r="A141" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B141" s="3" t="n">
         <v>11273</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="D141" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B142" s="2" t="n">
+      <c r="A142" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B142" s="3" t="n">
         <v>11274</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="D142" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B143" s="2" t="n">
+      <c r="A143" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B143" s="3" t="n">
         <v>11275</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="D143" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B144" s="2" t="n">
+      <c r="A144" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B144" s="3" t="n">
         <v>11276</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D144" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B145" s="2" t="n">
+      <c r="A145" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B145" s="3" t="n">
         <v>11277</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D145" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B146" s="2" t="n">
+      <c r="A146" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B146" s="3" t="n">
         <v>11278</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D146" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B147" s="2" t="n">
+      <c r="A147" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B147" s="3" t="n">
         <v>11279</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D147" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B148" s="2" t="n">
+      <c r="A148" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B148" s="3" t="n">
         <v>11280</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D148" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B149" s="2" t="n">
+      <c r="A149" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B149" s="3" t="n">
         <v>11281</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="D149" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B150" s="2" t="n">
+      <c r="A150" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B150" s="3" t="n">
         <v>11282</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D150" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B151" s="2" t="n">
+      <c r="A151" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B151" s="3" t="n">
         <v>11283</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="D151" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B152" s="2" t="n">
+      <c r="A152" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B152" s="3" t="n">
         <v>11284</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D152" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B153" s="2" t="n">
+      <c r="A153" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B153" s="3" t="n">
         <v>11285</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="D153" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B154" s="2" t="n">
+      <c r="A154" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B154" s="3" t="n">
         <v>11286</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D154" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B155" s="2" t="n">
+      <c r="A155" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B155" s="3" t="n">
         <v>11287</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="D155" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B156" s="2" t="n">
+      <c r="A156" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B156" s="3" t="n">
         <v>11288</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="D156" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B157" s="2" t="n">
+      <c r="A157" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B157" s="3" t="n">
         <v>11289</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="D157" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B158" s="2" t="n">
+      <c r="A158" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B158" s="3" t="n">
         <v>11290</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D158" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B159" s="2" t="n">
+      <c r="A159" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B159" s="3" t="n">
         <v>11291</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D159" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B160" s="2" t="n">
+      <c r="A160" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B160" s="3" t="n">
         <v>11292</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D160" s="2" t="s">
+      <c r="D160" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B161" s="2" t="n">
+      <c r="A161" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B161" s="3" t="n">
         <v>11293</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D161" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="3"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="3"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="3"/>
+      <c r="B207" s="3"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/24-23.xlsx
+++ b/outputs/24-23.xlsx
@@ -477,7 +477,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -2740,282 +2740,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
-      <c r="C162" s="3"/>
-      <c r="D162" s="3"/>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3"/>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
-    </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="3"/>
-      <c r="B166" s="3"/>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-    </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3"/>
-      <c r="B167" s="3"/>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3"/>
-    </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3"/>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="3"/>
-      <c r="B169" s="3"/>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3"/>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
-      <c r="C174" s="3"/>
-      <c r="D174" s="3"/>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3"/>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3"/>
-    </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
-    </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
-    </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
-      <c r="C183" s="3"/>
-      <c r="D183" s="3"/>
-    </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3"/>
-      <c r="B184" s="3"/>
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3"/>
-      <c r="B186" s="3"/>
-      <c r="C186" s="3"/>
-      <c r="D186" s="3"/>
-    </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3"/>
-      <c r="B187" s="3"/>
-      <c r="C187" s="3"/>
-      <c r="D187" s="3"/>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="3"/>
-      <c r="B188" s="3"/>
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
-    </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="3"/>
-      <c r="B191" s="3"/>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3"/>
-      <c r="B192" s="3"/>
-      <c r="C192" s="3"/>
-      <c r="D192" s="3"/>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="3"/>
-      <c r="B193" s="3"/>
-      <c r="C193" s="3"/>
-      <c r="D193" s="3"/>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3"/>
-      <c r="B194" s="3"/>
-      <c r="C194" s="3"/>
-      <c r="D194" s="3"/>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="3"/>
-      <c r="B195" s="3"/>
-      <c r="C195" s="3"/>
-      <c r="D195" s="3"/>
-    </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="3"/>
-      <c r="B196" s="3"/>
-      <c r="C196" s="3"/>
-      <c r="D196" s="3"/>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="3"/>
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
-      <c r="D197" s="3"/>
-    </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
-      <c r="C198" s="3"/>
-      <c r="D198" s="3"/>
-    </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="3"/>
-      <c r="B199" s="3"/>
-      <c r="C199" s="3"/>
-      <c r="D199" s="3"/>
-    </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="3"/>
-      <c r="B200" s="3"/>
-      <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-    </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="3"/>
-      <c r="B201" s="3"/>
-      <c r="C201" s="3"/>
-      <c r="D201" s="3"/>
-    </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="3"/>
-      <c r="B202" s="3"/>
-      <c r="C202" s="3"/>
-      <c r="D202" s="3"/>
-    </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="3"/>
-      <c r="B203" s="3"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-    </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="3"/>
-      <c r="B204" s="3"/>
-      <c r="C204" s="3"/>
-      <c r="D204" s="3"/>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="3"/>
-      <c r="B205" s="3"/>
-      <c r="C205" s="3"/>
-      <c r="D205" s="3"/>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="3"/>
-      <c r="B206" s="3"/>
-      <c r="C206" s="3"/>
-      <c r="D206" s="3"/>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="3"/>
-      <c r="B207" s="3"/>
-      <c r="C207" s="3"/>
-      <c r="D207" s="3"/>
-    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
